--- a/product-definitions/spreadsheet/radiation.xlsx
+++ b/product-definitions/spreadsheet/radiation.xlsx
@@ -200,7 +200,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -226,14 +226,9 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -251,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -266,32 +261,25 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -1593,7 +1581,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -1601,31 +1589,31 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -1633,42 +1621,42 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1678,7 +1666,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="5" t="s">
@@ -1686,31 +1674,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="5" t="s">
@@ -1718,651 +1706,660 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="6" t="s">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="B21" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="6" t="s">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="B22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="6" t="s">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="B23" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="6" t="s">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="B24" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26">
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="6" t="s">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="6" t="s">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="6" t="s">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="B29" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="6" t="s">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="B30" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="6" t="s">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="B31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="6" t="s">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="B32" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="6" t="s">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="B33" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="6" t="s">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="B34" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="6" t="s">
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="B35" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="6" t="s">
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="B36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="38">
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="6" t="s">
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="9" t="s">
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="B40" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="6" t="s">
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="B41" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="6" t="s">
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="B42" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="6" t="s">
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="B43" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="6" t="s">
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="B44" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="6" t="s">
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="B45" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="6" t="s">
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="B46" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="6" t="s">
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="B47" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="6" t="s">
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="B48" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="50">
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="6" t="s">
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="B51" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="9" t="s">
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="B52" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="6" t="s">
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="6" t="s">
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="B54" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="6" t="s">
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="B55" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="6" t="s">
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="B56" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C56" s="7">
+      <c r="C56" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="6" t="s">
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="B57" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="6" t="s">
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="B58" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="6" t="s">
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="B59" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="6" t="s">
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="B60" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="6" t="s">
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="6" t="s">
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="B63" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="6" t="s">
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="B64" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="6" t="s">
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="B65" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C65" s="10">
+      <c r="C65" s="8">
         <v>1.0</v>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="6" t="s">
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="B66" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="10"/>
-    </row>
-    <row r="67">
-      <c r="B67" s="6" t="s">
+      <c r="C66" s="8"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="B67" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" s="11" t="s">
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="B68" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="13" t="s">
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="B69" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C69" s="14" t="s">
+      <c r="C69" s="12" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="6" t="s">
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="6" t="s">
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="B72" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="6" t="s">
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="B73" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C73" s="6" t="s">
+      <c r="C73" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="6" t="s">
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="B74" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C74" s="10">
+      <c r="C74" s="8">
         <v>1.0</v>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" s="6" t="s">
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="B75" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C75" s="10"/>
-    </row>
-    <row r="76">
-      <c r="B76" s="6" t="s">
+      <c r="C75" s="8"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="B76" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" s="11" t="s">
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="B77" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C77" s="12" t="s">
+      <c r="C77" s="10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="13" t="s">
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="B78" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C78" s="14" t="s">
+      <c r="C78" s="12" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="6" t="s">
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" s="6" t="s">
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="B81" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" s="6" t="s">
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="B82" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C82" s="6" t="s">
+      <c r="C82" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" s="6" t="s">
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="B83" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C83" s="10">
+      <c r="C83" s="8">
         <v>1.0</v>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" s="6" t="s">
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="B84" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C84" s="10"/>
-    </row>
-    <row r="85">
-      <c r="B85" s="6" t="s">
+      <c r="C84" s="8"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="B85" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" s="11" t="s">
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="B86" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C86" s="12" t="s">
+      <c r="C86" s="10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="13" t="s">
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="B87" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C87" s="14" t="s">
+      <c r="C87" s="12" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="6" t="s">
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" s="6" t="s">
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="B90" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" s="6" t="s">
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="B91" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C91" s="6" t="s">
+      <c r="C91" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="92">
-      <c r="B92" s="6" t="s">
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="B92" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C92" s="10">
+      <c r="C92" s="8">
         <v>1.0</v>
       </c>
     </row>
-    <row r="93">
-      <c r="B93" s="6" t="s">
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="B93" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C93" s="10"/>
-    </row>
-    <row r="94">
-      <c r="B94" s="6" t="s">
+      <c r="C93" s="8"/>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="B94" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" s="11" t="s">
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="B95" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C95" s="12" t="s">
+      <c r="C95" s="10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="13" t="s">
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="B96" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C96" s="14" t="s">
+      <c r="C96" s="12" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="6" t="s">
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="99">
-      <c r="B99" s="6" t="s">
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="B99" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="100">
-      <c r="B100" s="6" t="s">
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="B100" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C100" s="6" t="s">
+      <c r="C100" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="101">
-      <c r="B101" s="6" t="s">
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="B101" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C101" s="10">
+      <c r="C101" s="8">
         <v>1.0</v>
       </c>
     </row>
-    <row r="102">
-      <c r="B102" s="6" t="s">
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="B102" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C102" s="10"/>
-    </row>
-    <row r="103">
-      <c r="B103" s="6" t="s">
+      <c r="C102" s="8"/>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="B103" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="104">
-      <c r="B104" s="11" t="s">
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="B104" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C104" s="12" t="s">
+      <c r="C104" s="10" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="105">
-      <c r="B105" s="13" t="s">
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="B105" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C105" s="15" t="s">
+      <c r="C105" s="12" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="6" t="s">
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="108">
-      <c r="B108" s="6" t="s">
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="B108" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="109">
-      <c r="B109" s="6" t="s">
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="B109" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C109" s="6" t="s">
+      <c r="C109" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="110">
-      <c r="B110" s="6" t="s">
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="B110" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C110" s="10">
+      <c r="C110" s="8">
         <v>1.0</v>
       </c>
     </row>
-    <row r="111">
-      <c r="B111" s="6" t="s">
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="B111" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C111" s="10"/>
-    </row>
-    <row r="112">
-      <c r="B112" s="6" t="s">
+      <c r="C111" s="8"/>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="B112" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="113">
-      <c r="B113" s="11" t="s">
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="B113" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C113" s="12" t="s">
+      <c r="C113" s="10" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="114">
-      <c r="B114" s="13" t="s">
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="B114" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C114" s="15" t="s">
+      <c r="C114" s="12" t="s">
         <v>55</v>
       </c>
     </row>
@@ -3252,8 +3249,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
